--- a/data/trans_dic/P36$cafe-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P36$cafe-Clase-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que desayuna, al menos, café, leche, té, chololate, yogurt,...</t>
+          <t>Población que desayuna, al menos, café, leche, té, chololate, yogurt,... (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>88,02; 93,14</t>
+          <t>87,89; 93,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>86,9; 93,26</t>
+          <t>86,81; 93,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>91,28; 96,16</t>
+          <t>91,38; 96,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>87,11; 93,87</t>
+          <t>87,13; 93,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>90,78; 96,45</t>
+          <t>90,34; 96,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,38; 95,78</t>
+          <t>90,41; 95,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,54; 92,83</t>
+          <t>88,68; 92,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>89,32; 93,68</t>
+          <t>89,68; 93,87</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>91,8; 95,31</t>
+          <t>91,59; 95,29</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>85,39; 92,05</t>
+          <t>84,86; 92,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>92,66; 97,34</t>
+          <t>92,79; 97,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>91,23; 96,32</t>
+          <t>91,36; 96,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>85,83; 92,26</t>
+          <t>86,04; 92,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>92,63; 97,43</t>
+          <t>92,47; 97,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>92,5; 96,83</t>
+          <t>92,02; 96,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>86,78; 91,38</t>
+          <t>86,65; 91,25</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>93,28; 96,88</t>
+          <t>93,54; 96,97</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>92,73; 95,95</t>
+          <t>92,51; 96,13</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>87,93; 93,16</t>
+          <t>88,16; 93,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>89,97; 94,22</t>
+          <t>90,08; 94,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>88,04; 93,27</t>
+          <t>87,92; 93,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>84,23; 93,48</t>
+          <t>84,01; 93,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>88,79; 95,3</t>
+          <t>88,81; 95,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>89,41; 96,99</t>
+          <t>88,91; 96,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>87,87; 92,64</t>
+          <t>88,01; 92,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>90,45; 94,07</t>
+          <t>90,42; 94,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>89,39; 93,52</t>
+          <t>89,33; 93,63</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>91,18; 94,12</t>
+          <t>91,24; 94,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>88,97; 92,69</t>
+          <t>88,97; 92,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>89,33; 92,61</t>
+          <t>89,24; 92,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>88,23; 92,62</t>
+          <t>88,08; 92,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>89,39; 93,86</t>
+          <t>89,75; 93,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,61; 94,23</t>
+          <t>90,69; 94,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,71; 93,12</t>
+          <t>90,71; 93,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>89,84; 92,56</t>
+          <t>89,97; 92,72</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>90,43; 92,95</t>
+          <t>90,46; 92,89</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>87,03; 93,69</t>
+          <t>86,97; 93,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>89,38; 94,21</t>
+          <t>89,24; 94,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>86,42; 91,36</t>
+          <t>86,34; 91,5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>91,93; 95,93</t>
+          <t>92,06; 96,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>93,67; 96,79</t>
+          <t>93,73; 96,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>92,14; 95,55</t>
+          <t>92,14; 95,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>90,76; 94,37</t>
+          <t>90,96; 94,4</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>92,63; 95,31</t>
+          <t>92,62; 95,36</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>90,26; 93,23</t>
+          <t>90,15; 93,13</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>89,21; 95,11</t>
+          <t>89,31; 95,06</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>82,72; 90,72</t>
+          <t>82,43; 90,83</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>79,36; 88,36</t>
+          <t>79,73; 88,28</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>90,58; 93,54</t>
+          <t>90,65; 93,61</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>91,12; 94,4</t>
+          <t>91,49; 94,66</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>92,16; 95,02</t>
+          <t>92,31; 95,14</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>90,86; 93,56</t>
+          <t>90,76; 93,44</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>90,18; 93,23</t>
+          <t>90,34; 93,32</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>90,19; 93,07</t>
+          <t>90,22; 93,16</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>90,42; 92,36</t>
+          <t>90,46; 92,55</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>90,49; 92,54</t>
+          <t>90,58; 92,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>89,77; 91,78</t>
+          <t>89,81; 91,81</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>90,54; 92,48</t>
+          <t>90,58; 92,44</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>92,79; 94,49</t>
+          <t>92,82; 94,47</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,74; 94,41</t>
+          <t>92,73; 94,39</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,82; 92,19</t>
+          <t>90,85; 92,18</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>91,89; 93,21</t>
+          <t>91,86; 93,18</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>91,58; 92,88</t>
+          <t>91,59; 92,89</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que desayuna, al menos, café, leche, té, chololate, yogurt,...</t>
+          <t>Población que desayuna, al menos, café, leche, té, chololate, yogurt,... (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>416216; 440436</t>
+          <t>415620; 441025</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>379932; 407735</t>
+          <t>379540; 407788</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>391688; 412624</t>
+          <t>392094; 412687</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>267154; 287892</t>
+          <t>267216; 287531</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>284397; 302187</t>
+          <t>283031; 301785</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>313683; 332394</t>
+          <t>313785; 332038</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>690260; 723636</t>
+          <t>691306; 724132</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>670314; 703037</t>
+          <t>673048; 704489</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>712490; 739743</t>
+          <t>710852; 739583</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>311812; 336119</t>
+          <t>309885; 336466</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>386166; 405700</t>
+          <t>386713; 406140</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>344131; 363360</t>
+          <t>344629; 362994</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>318262; 342105</t>
+          <t>319030; 341962</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>313099; 329315</t>
+          <t>312560; 329279</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>343312; 359403</t>
+          <t>341535; 359373</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>638693; 672533</t>
+          <t>637707; 671533</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>704075; 731222</t>
+          <t>706000; 731918</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>693976; 718055</t>
+          <t>692301; 719434</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>475173; 503425</t>
+          <t>476409; 503988</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>564613; 591284</t>
+          <t>565258; 591538</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>458540; 485776</t>
+          <t>457906; 484986</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>141330; 156850</t>
+          <t>140948; 156725</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>230968; 247891</t>
+          <t>231016; 247964</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>148528; 161127</t>
+          <t>147701; 160808</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>622239; 656039</t>
+          <t>623278; 654746</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>802867; 834995</t>
+          <t>802663; 835385</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>614073; 642415</t>
+          <t>613607; 643150</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1127257; 1163632</t>
+          <t>1128031; 1164181</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1030235; 1073338</t>
+          <t>1030239; 1072486</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1025994; 1063685</t>
+          <t>1024960; 1064924</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>629338; 660688</t>
+          <t>628284; 661151</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>683546; 717705</t>
+          <t>686313; 717032</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>748318; 778247</t>
+          <t>749018; 778965</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1768564; 1815425</t>
+          <t>1768388; 1813430</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1727160; 1779586</t>
+          <t>1729838; 1782548</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1785450; 1835161</t>
+          <t>1786036; 1834095</t>
         </is>
       </c>
     </row>
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>305102; 328421</t>
+          <t>304879; 327003</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>455564; 480167</t>
+          <t>454855; 480647</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>534862; 565471</t>
+          <t>534396; 566310</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>521016; 543729</t>
+          <t>521797; 544139</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>710527; 734190</t>
+          <t>710966; 733512</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>680218; 705419</t>
+          <t>680247; 705335</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>832564; 865654</t>
+          <t>834374; 865966</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1174753; 1208693</t>
+          <t>1174580; 1209425</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1224978; 1265238</t>
+          <t>1223440; 1263991</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>266023; 283617</t>
+          <t>266315; 283463</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>220758; 242117</t>
+          <t>219981; 242420</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>227870; 253733</t>
+          <t>228931; 253488</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1131105; 1168033</t>
+          <t>1131962; 1168976</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1010880; 1047210</t>
+          <t>1014926; 1050128</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>995261; 1026089</t>
+          <t>996852; 1027379</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1405555; 1447345</t>
+          <t>1404089; 1445528</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1241025; 1283008</t>
+          <t>1243330; 1284235</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1232974; 1272346</t>
+          <t>1233331; 1273584</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2950955; 3014148</t>
+          <t>2952001; 3020397</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3091252; 3161230</t>
+          <t>3094060; 3158763</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3035821; 3103704</t>
+          <t>3037201; 3104868</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3054980; 3120320</t>
+          <t>3056344; 3118923</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3288389; 3348646</t>
+          <t>3289658; 3348177</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3272259; 3331257</t>
+          <t>3271828; 3330329</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6028291; 6118873</t>
+          <t>6030554; 6118746</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>6395657; 6487437</t>
+          <t>6393154; 6485321</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>6328533; 6418096</t>
+          <t>6329032; 6418553</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P36$cafe-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P36$cafe-Clase-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>87,89; 93,26</t>
+          <t>87,86; 93,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>86,81; 93,27</t>
+          <t>86,79; 92,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>91,38; 96,18</t>
+          <t>91,19; 96,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>87,13; 93,76</t>
+          <t>86,92; 93,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>90,34; 96,33</t>
+          <t>90,94; 96,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,41; 95,67</t>
+          <t>90,25; 95,72</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,68; 92,89</t>
+          <t>88,73; 92,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>89,68; 93,87</t>
+          <t>89,74; 93,93</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>91,59; 95,29</t>
+          <t>91,77; 95,41</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>84,86; 92,14</t>
+          <t>85,13; 91,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>92,79; 97,45</t>
+          <t>92,77; 97,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>91,36; 96,23</t>
+          <t>91,1; 96,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>86,04; 92,22</t>
+          <t>86,15; 92,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>92,47; 97,42</t>
+          <t>92,39; 97,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>92,02; 96,82</t>
+          <t>92,45; 97,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>86,65; 91,25</t>
+          <t>86,64; 91,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>93,54; 96,97</t>
+          <t>93,54; 96,89</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>92,51; 96,13</t>
+          <t>92,51; 95,87</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>88,16; 93,27</t>
+          <t>87,89; 93,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>90,08; 94,26</t>
+          <t>90,07; 94,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>87,92; 93,12</t>
+          <t>87,83; 93,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>84,01; 93,41</t>
+          <t>84,3; 93,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>88,81; 95,32</t>
+          <t>88,15; 95,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>88,91; 96,8</t>
+          <t>89,51; 96,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>88,01; 92,46</t>
+          <t>88,17; 92,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>90,42; 94,11</t>
+          <t>90,42; 94,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>89,33; 93,63</t>
+          <t>89,19; 93,32</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>91,24; 94,17</t>
+          <t>91,17; 94,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>88,97; 92,62</t>
+          <t>89,21; 92,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>89,24; 92,72</t>
+          <t>89,34; 92,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>88,08; 92,69</t>
+          <t>88,32; 92,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>89,75; 93,77</t>
+          <t>89,76; 93,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,69; 94,32</t>
+          <t>90,59; 94,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,71; 93,02</t>
+          <t>90,5; 93,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>89,97; 92,72</t>
+          <t>89,96; 92,61</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>90,46; 92,89</t>
+          <t>90,51; 92,84</t>
         </is>
       </c>
     </row>
@@ -1118,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>86,97; 93,28</t>
+          <t>87,01; 93,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>89,24; 94,3</t>
+          <t>88,97; 93,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>86,34; 91,5</t>
+          <t>86,39; 91,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>92,06; 96,01</t>
+          <t>91,82; 96,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>93,73; 96,7</t>
+          <t>93,79; 96,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>92,14; 95,54</t>
+          <t>92,13; 95,65</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>90,96; 94,4</t>
+          <t>90,86; 94,22</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>92,62; 95,36</t>
+          <t>92,48; 95,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>90,15; 93,13</t>
+          <t>90,07; 93,26</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>89,31; 95,06</t>
+          <t>89,37; 95,06</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>82,43; 90,83</t>
+          <t>82,72; 90,83</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>79,73; 88,28</t>
+          <t>79,33; 88,64</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>90,65; 93,61</t>
+          <t>90,63; 93,5</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>91,49; 94,66</t>
+          <t>91,5; 94,61</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>92,31; 95,14</t>
+          <t>92,02; 95,02</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>90,76; 93,44</t>
+          <t>90,81; 93,49</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>90,34; 93,32</t>
+          <t>90,32; 93,27</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>90,22; 93,16</t>
+          <t>90,06; 93,16</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>90,46; 92,55</t>
+          <t>90,4; 92,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>90,58; 92,47</t>
+          <t>90,56; 92,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>89,81; 91,81</t>
+          <t>89,68; 91,8</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>90,58; 92,44</t>
+          <t>90,63; 92,56</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>92,82; 94,47</t>
+          <t>92,75; 94,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,73; 94,39</t>
+          <t>92,71; 94,4</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,85; 92,18</t>
+          <t>90,83; 92,22</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>91,86; 93,18</t>
+          <t>91,97; 93,2</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>91,59; 92,89</t>
+          <t>91,59; 92,87</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>415620; 441025</t>
+          <t>415468; 441489</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>379540; 407788</t>
+          <t>379450; 406419</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>392094; 412687</t>
+          <t>391276; 412790</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>267216; 287531</t>
+          <t>266558; 287908</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>283031; 301785</t>
+          <t>284923; 302136</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>313785; 332038</t>
+          <t>313206; 332184</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>691306; 724132</t>
+          <t>691731; 723950</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>673048; 704489</t>
+          <t>673490; 704960</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>710852; 739583</t>
+          <t>712290; 740560</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>309885; 336466</t>
+          <t>310865; 335648</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>386713; 406140</t>
+          <t>386623; 406140</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>344629; 362994</t>
+          <t>343666; 362689</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>319030; 341962</t>
+          <t>319423; 342360</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>312560; 329279</t>
+          <t>312296; 329234</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>341535; 359373</t>
+          <t>343129; 360069</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>637707; 671533</t>
+          <t>637601; 672686</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>706000; 731918</t>
+          <t>706056; 731342</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>692301; 719434</t>
+          <t>692355; 717455</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>476409; 503988</t>
+          <t>474934; 503107</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>565258; 591538</t>
+          <t>565248; 591944</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>457906; 484986</t>
+          <t>457428; 486583</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>140948; 156725</t>
+          <t>141436; 157007</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>231016; 247964</t>
+          <t>229316; 247950</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>147701; 160808</t>
+          <t>148702; 160978</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>623278; 654746</t>
+          <t>624361; 655814</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>802663; 835385</t>
+          <t>802612; 835036</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>613607; 643150</t>
+          <t>612684; 641056</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1128031; 1164181</t>
+          <t>1127119; 1163150</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1030239; 1072486</t>
+          <t>1032935; 1072719</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1024960; 1064924</t>
+          <t>1026162; 1064409</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>628284; 661151</t>
+          <t>629964; 660509</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>686313; 717032</t>
+          <t>686368; 716854</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>749018; 778965</t>
+          <t>748134; 777650</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1768388; 1813430</t>
+          <t>1764379; 1815319</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1729838; 1782548</t>
+          <t>1729590; 1780575</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1786036; 1834095</t>
+          <t>1786974; 1833139</t>
         </is>
       </c>
     </row>
@@ -2291,54 +2291,54 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>304879; 327003</t>
+          <t>305006; 327603</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>454855; 480647</t>
+          <t>453447; 478784</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>534396; 566310</t>
+          <t>534665; 566489</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>521797; 544139</t>
+          <t>520427; 544122</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>710966; 733512</t>
+          <t>711423; 735002</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>680247; 705335</t>
+          <t>680142; 706158</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>834374; 865966</t>
+          <t>833443; 864337</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1174580; 1209425</t>
+          <t>1172866; 1207593</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1223440; 1263991</t>
+          <t>1222427; 1265652</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>266315; 283463</t>
+          <t>266495; 283465</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>219981; 242420</t>
+          <t>220766; 242407</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>228931; 253488</t>
+          <t>227804; 254516</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1131962; 1168976</t>
+          <t>1131807; 1167605</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1014926; 1050128</t>
+          <t>1015061; 1049561</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>996852; 1027379</t>
+          <t>993756; 1026062</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1404089; 1445528</t>
+          <t>1404821; 1446205</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1243330; 1284235</t>
+          <t>1242952; 1283603</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1233331; 1273584</t>
+          <t>1231171; 1273457</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2952001; 3020397</t>
+          <t>2950074; 3015023</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3094060; 3158763</t>
+          <t>3093657; 3161749</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3037201; 3104868</t>
+          <t>3032746; 3104468</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3056344; 3118923</t>
+          <t>3057926; 3122980</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3289658; 3348177</t>
+          <t>3287009; 3345833</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3271828; 3330329</t>
+          <t>3271263; 3330694</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6030554; 6118746</t>
+          <t>6028664; 6120999</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>6393154; 6485321</t>
+          <t>6401259; 6486571</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>6329032; 6418553</t>
+          <t>6329023; 6417245</t>
         </is>
       </c>
     </row>
